--- a/PTKO_Agenda_v3.xlsx
+++ b/PTKO_Agenda_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zasch/codex/SitzungsBuddy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32467C0C-3B4F-A74F-BC55-006548D1A329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1C8837-753A-634A-9203-8DED53F8F794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="1560" windowWidth="28240" windowHeight="17240" xr2:uid="{6DF972DD-B225-C34E-AA9B-F95FA9B8C55C}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>Tag</t>
   </si>
   <si>
-    <t>Agenda interne Sitzung</t>
-  </si>
-  <si>
     <t>Frankfurt</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
   </si>
   <si>
     <t>135. PTKO</t>
+  </si>
+  <si>
+    <t>Agenda 10er Runde</t>
   </si>
 </sst>
 </file>
@@ -272,13 +272,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -625,23 +625,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="A1" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="10">
         <v>0.41666666666666669</v>
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="10">
         <f>D2+SUM(C6:C50)/1440</f>
@@ -666,7 +666,7 @@
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -687,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -695,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6">
         <v>15</v>
@@ -703,7 +703,7 @@
       <c r="D6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>D2</f>
         <v>0.41666666666666669</v>
       </c>
@@ -713,7 +713,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="6">
         <v>10</v>
@@ -721,7 +721,7 @@
       <c r="D7" s="8">
         <v>1</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <f>E6+C6/1440</f>
         <v>0.42708333333333337</v>
       </c>
@@ -731,7 +731,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="6">
         <v>25</v>
@@ -739,7 +739,7 @@
       <c r="D8" s="8">
         <v>1</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <f t="shared" ref="E8:E17" si="0">E7+C7/1440</f>
         <v>0.43402777777777779</v>
       </c>
@@ -749,7 +749,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6">
         <v>30</v>
@@ -757,7 +757,7 @@
       <c r="D9" s="8">
         <v>1</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <f t="shared" si="0"/>
         <v>0.4513888888888889</v>
       </c>
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="6">
         <v>45</v>
@@ -775,7 +775,7 @@
       <c r="D10" s="8">
         <v>1</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <f t="shared" si="0"/>
         <v>0.47222222222222221</v>
       </c>
@@ -786,7 +786,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6">
         <v>25</v>
@@ -794,7 +794,7 @@
       <c r="D11" s="8">
         <v>1</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <f t="shared" si="0"/>
         <v>0.50347222222222221</v>
       </c>
@@ -804,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="6">
         <v>20</v>
@@ -812,7 +812,7 @@
       <c r="D12" s="8">
         <v>1</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <f t="shared" si="0"/>
         <v>0.52083333333333337</v>
       </c>
@@ -822,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6">
         <v>10</v>
@@ -830,7 +830,7 @@
       <c r="D13" s="8">
         <v>1</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <f t="shared" si="0"/>
         <v>0.53472222222222221</v>
       </c>
@@ -848,7 +848,7 @@
       <c r="D14" s="8">
         <v>2</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <f t="shared" si="0"/>
         <v>0.54166666666666663</v>
       </c>
@@ -858,7 +858,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="6">
         <v>15</v>
@@ -866,7 +866,7 @@
       <c r="D15" s="8">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <f t="shared" si="0"/>
         <v>0.54861111111111105</v>
       </c>
@@ -876,7 +876,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="6">
         <v>10</v>
@@ -884,7 +884,7 @@
       <c r="D16" s="8">
         <v>2</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <f t="shared" si="0"/>
         <v>0.55902777777777768</v>
       </c>
@@ -894,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6">
         <v>5</v>
@@ -902,136 +902,136 @@
       <c r="D17" s="8">
         <v>2</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <f t="shared" si="0"/>
         <v>0.5659722222222221</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E18" s="14"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E19" s="14"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E20" s="14"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E21" s="14"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E22" s="14"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E23" s="14"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E24" s="14"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="14"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E26" s="14"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E27" s="14"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E28" s="14"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E29" s="14"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E30" s="14"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E31" s="14"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E32" s="14"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E33" s="14"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E34" s="14"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E35" s="14"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="36" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E36" s="14"/>
+      <c r="E36" s="12"/>
     </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E37" s="14"/>
+      <c r="E37" s="12"/>
     </row>
     <row r="38" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E38" s="14"/>
+      <c r="E38" s="12"/>
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E39" s="14"/>
+      <c r="E39" s="12"/>
     </row>
     <row r="40" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E40" s="14"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E41" s="14"/>
+      <c r="E41" s="12"/>
     </row>
     <row r="42" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E42" s="14"/>
+      <c r="E42" s="12"/>
     </row>
     <row r="43" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E43" s="14"/>
+      <c r="E43" s="12"/>
     </row>
     <row r="44" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E44" s="14"/>
+      <c r="E44" s="12"/>
     </row>
     <row r="45" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E45" s="14"/>
+      <c r="E45" s="12"/>
     </row>
     <row r="46" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E46" s="14"/>
+      <c r="E46" s="12"/>
     </row>
     <row r="47" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E47" s="14"/>
+      <c r="E47" s="12"/>
     </row>
     <row r="48" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E48" s="14"/>
+      <c r="E48" s="12"/>
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E49" s="14"/>
+      <c r="E49" s="12"/>
     </row>
     <row r="50" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E50" s="14"/>
+      <c r="E50" s="12"/>
     </row>
     <row r="51" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E51" s="14"/>
+      <c r="E51" s="12"/>
     </row>
     <row r="52" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E52" s="14"/>
+      <c r="E52" s="12"/>
     </row>
     <row r="53" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E53" s="14"/>
+      <c r="E53" s="12"/>
     </row>
     <row r="54" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E54" s="14"/>
+      <c r="E54" s="12"/>
     </row>
     <row r="55" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E55" s="14"/>
+      <c r="E55" s="12"/>
     </row>
     <row r="56" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E56" s="14"/>
+      <c r="E56" s="12"/>
     </row>
     <row r="57" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E57" s="14"/>
+      <c r="E57" s="12"/>
     </row>
     <row r="58" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E58" s="14"/>
+      <c r="E58" s="12"/>
     </row>
     <row r="59" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E59" s="14"/>
+      <c r="E59" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
